--- a/metadata/docx_variable_audit.xlsx
+++ b/metadata/docx_variable_audit.xlsx
@@ -4542,37 +4542,37 @@
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Partially implemented – active all-residential proxy only</t>
+          <t>Partially implemented – ACS annual availability and HUD/USPS quarterly proxies; monthly listings unavailable</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>hud_usps_ncwm_quarterly</t>
+          <t>census_acs_5year_b25003|census_acs_5year_b25004|hud_usps_ncwm_quarterly</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>usps_total_residential_addresses|usps_short_term_vacant_residential_addresses|usps_long_term_vacant_residential_addresses|usps_vacant_residential_addresses|usps_no_stat_residential_addresses|usps_active_residential_addresses|usps_residential_vacancy_rate|usps_residential_no_stat_rate</t>
+          <t>acs_renter_occupied_units|acs_renter_occupied_units_moe|acs_for_rent_vacant_units|acs_for_rent_vacant_units_moe|acs_rental_availability_rate|usps_total_residential_addresses|usps_short_term_vacant_residential_addresses|usps_long_term_vacant_residential_addresses|usps_vacant_residential_addresses|usps_no_stat_residential_addresses|usps_active_residential_addresses|usps_residential_vacancy_rate|usps_residential_no_stat_rate</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>analytics.fact_housing_observation|data/restricted/hud_usps/active/ca_county_quarterly.parquet|data/restricted/hud_usps/active/la_tract_2020_quarterly.parquet|data/restricted/hud_usps/active/la_postal_zip_county_part_quarterly.parquet|data/restricted/hud_usps/active/long_observations_with_lineage.parquet</t>
+          <t>analytics.fact_housing_observation|analytics.county_annual_controls|data/restricted/hud_usps/active/ca_county_quarterly.parquet|data/restricted/hud_usps/active/la_tract_2020_quarterly.parquet|data/restricted/hud_usps/active/la_postal_zip_county_part_quarterly.parquet|data/restricted/hud_usps/active/long_observations_with_lineage.parquet</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>usps_total_residential_addresses|usps_short_term_vacant_residential_addresses|usps_long_term_vacant_residential_addresses|usps_vacant_residential_addresses|usps_no_stat_residential_addresses|usps_active_residential_addresses|usps_residential_vacancy_rate|usps_residential_no_stat_rate</t>
+          <t>acs_renter_occupied_units|acs_renter_occupied_units_moe|acs_for_rent_vacant_units|acs_for_rent_vacant_units_moe|acs_rental_availability_rate|usps_total_residential_addresses|usps_short_term_vacant_residential_addresses|usps_long_term_vacant_residential_addresses|usps_vacant_residential_addresses|usps_no_stat_residential_addresses|usps_active_residential_addresses|usps_residential_vacancy_rate|usps_residential_no_stat_rate</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>active all-residential proxy</t>
+          <t>separate annual and quarterly proxies</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>The eight active HUD-USPS variables are native-quarterly only. The vacancy proxy is (short-term vacant + long-term vacant) / total residential addresses, while no-stat remains a separate diagnostic. Direct provider components are observed at standardized 2020-tract geography; California county aggregates are constructed, and Los Angeles County postal-ZIP county-parts are modeled with the fixed 2026 Q1 crosswalk. Detailed tract and modeled ZIP-part derivatives remain access-controlled under the HUD-USPS sublicense. This is not true rental-listing inventory; ZORI is not inventory (it is a rent index), and Redfin for-sale active listings are not a valid substitute. The former derived package file was deleted; its historical quarantine manifest is superseded and is not an active input.</t>
+          <t>The annual ACS rental-availability proxy is for-rent vacant units divided by renter-occupied plus for-rent vacant units, using matched B25003 and B25004 estimates. Component 90% margins of error are retained, and unreliable county ratios are suppressed. Direct ACS counts and margins of error are retained at county and ZCTA geography; ZCTAs are not postal ZIPs. The eight active HUD-USPS variables are native-quarterly only and remain a separate all-residential measure. The vacancy proxy is (short-term vacant + long-term vacant) / total residential addresses, while no-stat remains a separate diagnostic. Direct provider components are observed at standardized 2020-tract geography; California county aggregates are constructed, and Los Angeles County postal-ZIP county-parts are modeled with the fixed 2026 Q1 crosswalk. Detailed tract and modeled ZIP-part derivatives remain access-controlled under the HUD-USPS sublicense. This is not true rental-listing inventory; ZORI is not inventory (it is a rent index), and Redfin for-sale active listings are not a valid substitute. The monthly rental-listing series remains missing at documented source and license acquisition. The former derived package file was deleted; its historical quarantine manifest is superseded and is not an active input.</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr"/>
@@ -4583,7 +4583,7 @@
         <v>1</v>
       </c>
       <c r="V28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W28" t="b">
         <v>1</v>
@@ -4598,11 +4598,11 @@
         <v>46112</v>
       </c>
       <c r="AA28" t="n">
-        <v>1768936</v>
+        <v>1770036</v>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>9256 missing of 1768936 fact rows</t>
+          <t>9256 missing of 1770036 fact rows</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -5785,7 +5785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5887,27 +5887,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>hud_usps_residential_vacancy_proxy_v2</t>
+          <t>acs_rental_availability_proxy_v1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>usps_residential_vacancy_rate</t>
+          <t>acs_rental_availability_rate</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>All-residential vacancy-proxy formula</t>
+          <t>Matched annual ACS rental-availability proxy</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>(short-term vacant residential addresses + long-term vacant residential addresses) / total residential addresses; rates remain ratios in [0, 1].</t>
+          <t>For the 2024 ACS five-year vintage, B25004 for-rent vacant units / (B25003 renter-occupied units + B25004 for-rent vacant units). Both component 90% margins of error are retained; the rate is suppressed when either component MOE is greater than or equal to its estimate. The annual value is not interpolated or expanded to monthly frequency.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>No-stat residential addresses remain a separate count and rate diagnostic and never enter the vacancy numerator. This is an all-residential address-status proxy, not rental-listing inventory.</t>
+          <t>This preserves a transparent annual rental-availability proxy with matched ACS universes and explicit reliability screening. It is not an active rental-listing stock, and it remains separate from the quarterly HUD-USPS all-residential proxy.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -5929,17 +5929,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Official active provenance</t>
+          <t>All-residential vacancy-proxy formula</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>provenance_status=official_raw_archive_rebuilt; 75 immutable official artifacts are indexed by metadata/hud_usps_source_manifest.csv, including 73 contiguous 2008 Q1-2026 Q1 NCWM responses, the 2026 Q1 tract-to-postal-ZIP crosswalk, and the 2020 Census California county reference.</t>
+          <t>(short-term vacant residential addresses + long-term vacant residential addresses) / total residential addresses; rates remain ratios in [0, 1].</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Every active observation is rebuilt from the verified official archive. The former derived package file was deleted; only its historical, superseded quarantine manifest remains, and it is not an active input.</t>
+          <t>No-stat residential addresses remain a separate count and rate diagnostic and never enter the vacancy numerator. This is an all-residential address-status proxy, not rental-listing inventory.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -5961,17 +5961,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Geography-specific construction</t>
+          <t>Official active provenance</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Provider component fields are direct at standardized 2020-tract geography; California county values are constructed from complete tract components; Los Angeles County postal-ZIP county-part values are modeled with the fixed 2026 Q1 crosswalk.</t>
+          <t>provenance_status=official_raw_archive_rebuilt; 75 immutable official artifacts are indexed by metadata/hud_usps_source_manifest.csv, including 73 contiguous 2008 Q1-2026 Q1 NCWM responses, the 2026 Q1 tract-to-postal-ZIP crosswalk, and the 2020 Census California county reference.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Modeled ZIP rows describe only the Los Angeles County portion of USPS postal ZIPs. They are neither whole postal ZIPs nor Census ZCTAs, and no tract percentages are averaged.</t>
+          <t>Every active observation is rebuilt from the verified official archive. The former derived package file was deleted; only its historical, superseded quarantine manifest remains, and it is not an active input.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -5988,22 +5988,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>usps_residential_no_stat_rate</t>
+          <t>usps_residential_vacancy_rate</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Quarterly-only restricted diagnostic</t>
+          <t>Geography-specific construction</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>No-stat / total remains a separate native-quarterly diagnostic. The eight active variables are stored in the common fact and restricted native-quarterly tables; they are not expanded into observed months.</t>
+          <t>Provider component fields are direct at standardized 2020-tract geography; California county values are constructed from complete tract components; Los Angeles County postal-ZIP county-part values are modeled with the fixed 2026 Q1 crosswalk.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Licensed tract and modeled postal-ZIP county-part observations and derivatives remain access-controlled under data/restricted/hud_usps/ and outside public exports under the HUD-USPS sublicense.</t>
+          <t>Modeled ZIP rows describe only the Los Angeles County portion of USPS postal ZIPs. They are neither whole postal ZIPs nor Census ZCTAs, and no tract percentages are averaged.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -6015,32 +6015,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>acs_implied_mortgage_debt_proxy_legacy_v0</t>
+          <t>hud_usps_residential_vacancy_proxy_v2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>acs_implied_aggregate_mortgage_debt_proxy</t>
+          <t>usps_residential_no_stat_rate</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Legacy ACS B25106 table role</t>
+          <t>Quarterly-only restricted diagnostic</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Legacy scenario only: B25106 owner income x housing-cost-burden bins infer monthly owner housing costs; B25106 is not an observed mortgage balance and is not the authoritative Version A method.</t>
+          <t>No-stat / total remains a separate native-quarterly diagnostic. The eight active variables are stored in the common fact and restricted native-quarterly tables; they are not expanded into observed months.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Retained in facts for reproducibility and labeled legacy; do not select it in place of the Version A _benchmark variables.</t>
+          <t>Licensed tract and modeled postal-ZIP county-part observations and derivatives remain access-controlled under data/restricted/hud_usps/ and outside public exports under the HUD-USPS sublicense.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>legacy</t>
+          <t>active</t>
         </is>
       </c>
     </row>
@@ -6057,17 +6057,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Income bin midpoints</t>
+          <t>Legacy ACS B25106 table role</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>10000; 27500; 42500; 62500; 112500</t>
+          <t>Legacy scenario only: B25106 owner income x housing-cost-burden bins infer monthly owner housing costs; B25106 is not an observed mortgage balance and is not the authoritative Version A method.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Closed bins use midpoint values. The open-ended $75k+ bin uses $112,500, or 1.5 times the lower bound, as a transparent conservative top-bin assumption.</t>
+          <t>Retained in facts for reproducibility and labeled legacy; do not select it in place of the Version A _benchmark variables.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -6089,17 +6089,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Housing-cost-burden midpoints</t>
+          <t>Income bin midpoints</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.10 for &lt;20%; 0.25 for 20-29%; 0.40 for 30%+</t>
+          <t>10000; 27500; 42500; 62500; 112500</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Closed or semi-closed categories use practical midpoints; 30%+ uses 40% to avoid implying unlimited burden while retaining high-burden signal.</t>
+          <t>Closed bins use midpoint values. The open-ended $75k+ bin uses $112,500, or 1.5 times the lower bound, as a transparent conservative top-bin assumption.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -6121,17 +6121,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Debt-service share of ACS owner housing cost</t>
+          <t>Housing-cost-burden midpoints</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.10 for &lt;20%; 0.25 for 20-29%; 0.40 for 30%+</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ACS owner housing costs include non-debt items such as taxes, insurance, utilities, and fees; 80% assigns most but not all inferred owner cost to mortgage debt service.</t>
+          <t>Closed or semi-closed categories use practical midpoints; 30%+ uses 40% to avoid implying unlimited burden while retaining high-burden signal.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mortgage-rate assumption</t>
+          <t>Debt-service share of ACS owner housing cost</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Mean Freddie Mac PMMS monthly-average 30-year fixed rate over the ACS five-year estimate window.</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>The ACS 5-year estimate pools observations over five years; using the same window avoids using only one endpoint-year rate.</t>
+          <t>ACS owner housing costs include non-debt items such as taxes, insurance, utilities, and fees; 80% assigns most but not all inferred owner cost to mortgage debt service.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -6185,17 +6185,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remaining amortization term</t>
+          <t>Mortgage-rate assumption</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>25 years</t>
+          <t>Mean Freddie Mac PMMS monthly-average 30-year fixed rate over the ACS five-year estimate window.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Outstanding balances are on existing mortgages, not all new 30-year loans; 25 years is a transparent middle-ground remaining-term assumption.</t>
+          <t>The ACS 5-year estimate pools observations over five years; using the same window avoids using only one endpoint-year rate.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -6217,17 +6217,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Allocation of B25081 mortgaged units</t>
+          <t>Remaining amortization term</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>B25081 owner-with-mortgage count is allocated across positive-income B25106 bins proportional to B25106 owner unit counts.</t>
+          <t>25 years</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>B25106 bins are not mortgage-status-specific. This forces aggregate mortgaged units to match the directly observed B25081 count while preserving the B25106 income/burden distribution.</t>
+          <t>Outstanding balances are on existing mortgages, not all new 30-year loans; 25 years is a transparent middle-ground remaining-term assumption.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -6249,17 +6249,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Zero/negative income handling</t>
+          <t>Allocation of B25081 mortgaged units</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>B25106 zero/negative-income owner units are preserved as an input but excluded from payment-to-balance inference.</t>
+          <t>B25081 owner-with-mortgage count is allocated across positive-income B25106 bins proportional to B25106 owner unit counts.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>A positive income midpoint is required to infer monthly owner housing cost from cost-burden percentages.</t>
+          <t>B25106 bins are not mortgage-status-specific. This forces aggregate mortgaged units to match the directly observed B25081 count while preserving the B25106 income/burden distribution.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -6271,59 +6271,59 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>eviction_lab_county_estimates_v1</t>
+          <t>acs_implied_mortgage_debt_proxy_legacy_v0</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>eviction_lab_filings_estimate_annual</t>
+          <t>acs_implied_aggregate_mortgage_debt_proxy</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LA eviction-source choice</t>
+          <t>Zero/negative income handling</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Use official Eviction Lab annual county modeled estimates for Los Angeles County because ETS and the observed/validated county analysis files do not provide LA County rows.</t>
+          <t>B25106 zero/negative-income owner units are preserved as an input but excluded from payment-to-balance inference.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>This preserves the expected Eviction Lab source family without silently substituting another geography, and keeps the limitation explicit for modeling.</t>
+          <t>A positive income midpoint is required to infer monthly owner housing cost from cost-burden percentages.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>legacy</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>eviction_lab_county_rate_v1</t>
+          <t>eviction_lab_county_estimates_v1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>eviction_lab_filings_rate_estimate_annual</t>
+          <t>eviction_lab_filings_estimate_annual</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Annual rate denominator</t>
+          <t>LA eviction-source choice</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>filings_estimate divided by Eviction Lab renting_hh, multiplied by 100.</t>
+          <t>Use official Eviction Lab annual county modeled estimates for Los Angeles County because ETS and the observed/validated county analysis files do not provide LA County rows.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>A rate normalizes the trend for renter-household base changes while using only fields published in the same official Eviction Lab file.</t>
+          <t>This preserves the expected Eviction Lab source family without silently substituting another geography, and keeps the limitation explicit for modeling.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -6340,25 +6340,57 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>eviction_lab_filings_rate_estimate_annual</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Annual rate denominator</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>filings_estimate divided by Eviction Lab renting_hh, multiplied by 100.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>A rate normalizes the trend for renter-household base changes while using only fields published in the same official Eviction Lab file.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>eviction_lab_county_rate_v1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>eviction_lab_households_threatened_rate_estimate_annual</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Annual rate denominator</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>hh_threat_estimate divided by Eviction Lab renting_hh, multiplied by 100.</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>A rate normalizes households-threatened estimates for renter-household base changes while using only fields published in the same official Eviction Lab file.</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>active</t>
         </is>

--- a/metadata/docx_variable_audit.xlsx
+++ b/metadata/docx_variable_audit.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Use Zillow ZORI and exclude geographies by construction-year share (post-1995 / post-2005 proxy) or interact with policy exposure.</t>
+          <t>Use Zillow ZORI with the methodology-listed ACS B25032/B25127 renter structure and year-built inputs. Preserve lower/upper structural exposure bounds because published ACS bins cannot recover an exact rolling 15-year cutoff; construct an exact point exposure only after a complete dated property-level policy and exemption crosswalk is available.</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Eviction Lab ETS where available; otherwise annual filings with interpolation.</t>
+          <t>Use Eviction Lab ETS only where the official release contains the geography; otherwise retain official annual modeled estimates at native annual frequency without interpolation.</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Proxy with lagged multifamily permits (5+) using completion lag structure; lags uncertain.</t>
+          <t>Use separately labeled Central and Slow distributed-lag scenarios from 5+ unit permits, with the approved bucket weights and complete-lag missingness rules.</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Build pipeline stock: cumulative MF permits minus assumed completions over rolling window.</t>
+          <t>Build separately labeled Central and Slow stock-flow scenarios from current permits, scenario completions, and every surviving pre-output permit cohort; never initialize the opening stock to zero.</t>
         </is>
       </c>
     </row>
@@ -1964,37 +1964,37 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Proxy implemented</t>
+          <t>Partially implemented</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>census_acs5_finance|census_acs5_pums_housing_ca|census_tract_to_puma_2010|census_tract_to_puma_2020|fhfa_nmdb_joint_distribution|fhfa_nmdb_ca_upb|freddie_mac_pmms|bls_cpi_u_us_city_average</t>
+          <t>census_acs5_finance|census_acs5_pums_housing_ca|census_tract_to_puma_2010|census_tract_to_puma_2020|fhfa_nmdb_joint_distribution|fhfa_nmdb_ca_upb|freddie_mac_pmms|bls_cpi_u_us_city_average|census_sipp_2025_state_wealth_2024</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>acs_implied_owner_occupied_home_equity_mortgaged_benchmark|acs_implied_owner_occupied_home_equity_all_benchmark|acs_implied_owner_occupied_home_equity_mortgaged_real_2024_benchmark|acs_implied_owner_occupied_home_equity_all_real_2024_benchmark</t>
+          <t>acs_implied_owner_occupied_home_equity_mortgaged_pmms_20y_scenario_benchmark|acs_implied_owner_occupied_home_equity_mortgaged_pmms_25y_scenario_benchmark|acs_implied_owner_occupied_home_equity_mortgaged_pmms_30y_scenario_benchmark|acs_implied_owner_occupied_home_equity_all_pmms_20y_scenario_benchmark|acs_implied_owner_occupied_home_equity_all_pmms_25y_scenario_benchmark|acs_implied_owner_occupied_home_equity_all_pmms_30y_scenario_benchmark|acs_implied_owner_occupied_home_equity_mortgaged_benchmark|acs_implied_owner_occupied_home_equity_all_benchmark|acs_implied_owner_occupied_home_equity_mortgaged_real_2024_benchmark|acs_implied_owner_occupied_home_equity_all_real_2024_benchmark|sipp_ca_aggregate_positive_home_equity_sensitivity</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>analytics.housing_finance_benchmark</t>
+          <t>analytics.housing_finance_benchmark|analytics.state_annual_controls</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>acs_implied_owner_occupied_home_equity_all_benchmark</t>
+          <t>acs_implied_owner_occupied_home_equity_all_pmms_20y_scenario_benchmark|acs_implied_owner_occupied_home_equity_all_pmms_25y_scenario_benchmark|acs_implied_owner_occupied_home_equity_all_pmms_30y_scenario_benchmark|sipp_ca_aggregate_positive_home_equity_sensitivity</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>proxy</t>
+          <t>scenario sensitivity|published-table sensitivity|schema only</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Version A is authoritative: published ACS matched-universe owner values less exact-date California-calibrated first-mortgage debt, with mortgage-free value added in full for the all-owner measure. Calibrated debt and equity remain null when an exact-date, universe-compatible California NMDB UPB control is unavailable. The older B25106 midpoint proxy remains only as a labeled legacy modeled scenario.</t>
+          <t>The methodology-authorized raw PMMS 20/25/30-year debt sensitivities produce matching mortgaged-owner and all-owner equity scenarios for all 58 California counties. They are explicit uncalibrated scenarios. The official 2025 SIPP state wealth table now also produces one separately labeled 2024 California positive-home-equity sensitivity of $4,913,341,020,000 from rounded published inputs. It is conditional on positive equity, truncates the conditional mean to net worth below the 99th percentile, and has no valid covariance-based aggregate standard error. It is not the preferred matched-universe county equity target. The calibrated nominal and real equity targets remain null until an exact-date, owner-occupied first-lien California UPB control is available. The older B25106 midpoint proxy remains only as a separately labeled legacy modeled scenario.</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -2008,7 +2008,7 @@
         <v>1</v>
       </c>
       <c r="W2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2" t="b">
         <v>1</v>
@@ -2020,16 +2020,16 @@
         <v>45657</v>
       </c>
       <c r="AA2" t="n">
-        <v>232</v>
+        <v>1</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>232 missing of 232 Version A benchmark rows</t>
+          <t>0 missing of 1 fact rows</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ready for data-collection use</t>
+          <t>Review documented limitation before modeling</t>
         </is>
       </c>
     </row>
@@ -2065,37 +2065,37 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Proxy implemented</t>
+          <t>Partially implemented</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>census_acs5_finance|census_acs5_pums_housing_ca|census_tract_to_puma_2010|census_tract_to_puma_2020|fhfa_nmdb_joint_distribution|fhfa_nmdb_ca_upb|freddie_mac_pmms</t>
+          <t>census_acs5_finance|census_acs5_pums_housing_ca|census_tract_to_puma_2010|census_tract_to_puma_2020|fhfa_nmdb_joint_distribution|fhfa_nmdb_ca_upb|freddie_mac_pmms|census_sipp_2025_state_debt_2024|census_ahs_2023_ca_table14a</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>acs_implied_first_mortgage_balance_raw_benchmark|acs_implied_first_mortgage_balance_cal_benchmark|acs_first_mortgage_debt_per_mortgaged_owner_unit_benchmark|acs_first_mortgage_debt_per_owner_unit_benchmark|acs_first_mortgage_debt_per_capita_benchmark|acs_first_mortgage_debt_to_owner_income_benchmark</t>
+          <t>acs_implied_first_mortgage_balance_raw_pmms_20y_sensitivity_benchmark|acs_implied_first_mortgage_balance_raw_pmms_25y_sensitivity_benchmark|acs_implied_first_mortgage_balance_raw_pmms_30y_sensitivity_benchmark|acs_implied_first_mortgage_balance_raw_benchmark|acs_implied_first_mortgage_balance_cal_benchmark|acs_first_mortgage_debt_per_mortgaged_owner_unit_benchmark|acs_first_mortgage_debt_per_owner_unit_benchmark|acs_first_mortgage_debt_per_capita_benchmark|acs_first_mortgage_debt_to_owner_income_benchmark|sipp_ca_aggregate_primary_residence_debt_sensitivity|ahs_ca_reported_case_primary_mortgage_outstanding_principal_proxy</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>analytics.housing_finance_benchmark</t>
+          <t>analytics.housing_finance_benchmark|analytics.state_annual_controls</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>acs_implied_first_mortgage_balance_cal_benchmark</t>
+          <t>acs_implied_first_mortgage_balance_cal_benchmark|sipp_ca_aggregate_primary_residence_debt_sensitivity|ahs_ca_reported_case_primary_mortgage_outstanding_principal_proxy</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>proxy</t>
+          <t>scenario sensitivity|published-table sensitivity|reported-case public proxy|schema only</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Version A is authoritative: direct ACS B25089/B25081 levels, weighted PUMS first-mortgage P&amp;I parameters, an exact-date joint NMDB rate-term distribution, and a compatible California UPB control. PMMS is only a labeled sensitivity fallback. Calibrated values remain null without the compatible control. The older B25106 midpoint/80%/25-year proxy is legacy.</t>
+          <t>Version A publishes explicit raw PMMS 20/25/30-year debt sensitivities for all 58 California counties while retaining the composite raw envelope. The official 2025 SIPP state debt table adds a broader 2024 California Home Debt sensitivity of $1,627,458,504,000. The official 2023 California AHS Table 14A adds a reported-case primary-mortgage proxy of $1,413,679,720,000 from 3,381,200 reported-bin households times the $418,100 conditional mean. AHS excludes 1,203,800 regular-mortgage households with no reported balance (26.2540 percent), does not make a missing-at-random extrapolation, may not match legal first-lien status, and has no covariance-based aggregate uncertainty measure. Neither public sensitivity matches the current Version A target universe and 2022-07-01 reference date exactly. Calibrated debt and normalized ratios remain null; the older B25106 proxy remains a separate legacy construction.</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -2109,28 +2109,28 @@
         <v>1</v>
       </c>
       <c r="W3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3" t="b">
         <v>1</v>
       </c>
       <c r="Y3" s="1" t="n">
-        <v>45657</v>
+        <v>45291</v>
       </c>
       <c r="Z3" s="1" t="n">
         <v>45657</v>
       </c>
       <c r="AA3" t="n">
-        <v>348</v>
+        <v>2</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>290 missing of 348 Version A benchmark rows</t>
+          <t>0 missing of 2 fact rows</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ready for data-collection use</t>
+          <t>Review documented limitation before modeling</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,20 @@
       <c r="X4" t="b">
         <v>1</v>
       </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+      <c r="Y4" s="1" t="n">
+        <v>40939</v>
+      </c>
+      <c r="Z4" s="1" t="n">
+        <v>46173</v>
+      </c>
       <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="inlineStr"/>
+        <v>519</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>0 missing of 519 panel cells</t>
+        </is>
+      </c>
       <c r="AC4" t="inlineStr">
         <is>
           <t>Ready for data-collection use</t>
@@ -2300,12 +2308,20 @@
       <c r="X5" t="b">
         <v>1</v>
       </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
+      <c r="Y5" s="1" t="n">
+        <v>40939</v>
+      </c>
+      <c r="Z5" s="1" t="n">
+        <v>46173</v>
+      </c>
       <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="inlineStr"/>
+        <v>519</v>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>0 missing of 519 panel cells</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
           <t>Ready for data-collection use</t>
@@ -2389,12 +2405,20 @@
       <c r="X6" t="b">
         <v>1</v>
       </c>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
+      <c r="Y6" s="1" t="n">
+        <v>40939</v>
+      </c>
+      <c r="Z6" s="1" t="n">
+        <v>46173</v>
+      </c>
       <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="inlineStr"/>
+        <v>519</v>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>0 missing of 519 panel cells</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
           <t>Ready for data-collection use</t>
@@ -2433,21 +2457,37 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Not implemented</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ca_doi_residential_property_part_i|ca_dir_california_cpi</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>ca_homeowners_written_premium|ca_homeowners_written_exposures|ca_homeowners_avg_written_premium|ca_cpi_u_all_items_annual|ca_homeowners_avg_written_premium_real|ca_homeowners_avg_written_premium_yoy|ca_homeowners_avg_written_premium_monthly_control</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>analytics.fact_housing_observation|analytics.state_annual_controls|analytics.state_monthly_controls</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>ca_homeowners_avg_written_premium|ca_cpi_u_all_items_annual|ca_homeowners_avg_written_premium_real|ca_homeowners_avg_written_premium_monthly_control</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>deferred</t>
+          <t>observed annual|constructed annual|carried annual control</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>The sheet specifies a CA state NAIC series; NAIC/state homeowners-insurance data is not loaded yet.</t>
+          <t>Official California DOI Homeowners Multi-Peril annual average premium is deflated with official California DIR annual CPI-U as nominal_premium_year * CPI_2023 / CPI_year. The 16 real values cover 2008-2023 and the 2023 real value equals nominal by construction. CPI and real premium remain annual. The separately authorized nominal calendar-year monthly control is flagged carried_annual_control and mixed_frequency_control with is_interpolated=false; it is neither observed monthly nor Los Angeles County insurance.</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -2455,26 +2495,34 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Y7" s="1" t="n">
+        <v>20454</v>
+      </c>
+      <c r="Z7" s="1" t="n">
+        <v>46022</v>
+      </c>
       <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="inlineStr"/>
+        <v>311</v>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>0 missing of 311 fact rows</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Review documented limitation before modeling</t>
+          <t>Ready for data-collection use</t>
         </is>
       </c>
     </row>
@@ -2505,42 +2553,42 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Use Zillow ZORI and exclude geographies by construction-year share (post-1995 / post-2005 proxy) or interact with policy exposure.</t>
+          <t>Use Zillow ZORI with the methodology-listed ACS B25032/B25127 renter structure and year-built inputs. Preserve lower/upper structural exposure bounds because published ACS bins cannot recover an exact rolling 15-year cutoff; construct an exact point exposure only after a complete dated property-level policy and exemption crosswalk is available.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Not implemented</t>
+          <t>Partially implemented</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>zillow_county_zori_smoothed_sa|zillow_zip_zori_smoothed_sa</t>
+          <t>zillow_county_zori_smoothed_sa|zillow_zip_zori_smoothed_sa|census_acs_5year_b25032|census_acs_5year_b25127</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>zori_smoothed_sa</t>
+          <t>zori_smoothed_sa|acs_renter_occupied_1_unit_share|acs_renter_occupied_2_to_4_units_share|acs_renter_occupied_5_plus_units_share|acs_renter_occupied_mobile_other_share|acs_renter_recent_construction_share_lower_bound|acs_renter_recent_construction_share_upper_bound|noncontrolled_exposure_share_structural_proxy_lower_bound|noncontrolled_exposure_share_structural_proxy_upper_bound|exposure_adjusted_noncontrolled_rent_growth_structural_proxy_lower_bound|exposure_adjusted_noncontrolled_rent_growth_structural_proxy_upper_bound</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>analytics.county_monthly_panel|analytics.zip_monthly_panel</t>
+          <t>analytics.county_monthly_panel|analytics.zip_monthly_panel|analytics.county_annual_controls|analytics.zcta_annual_controls</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>zori</t>
+          <t>noncontrolled_exposure_share_structural_proxy_lower_bound|noncontrolled_exposure_share_structural_proxy_upper_bound|exposure_adjusted_noncontrolled_rent_growth_structural_proxy_lower_bound|exposure_adjusted_noncontrolled_rent_growth_structural_proxy_upper_bound</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>proxy input</t>
+          <t>observed rent index|constructed structural proxy bounds|annual exposure-scaled sensitivity</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>ZORI is loaded, but the sheet workaround also requires construction-year/rent-control exposure filters that are not implemented.</t>
+          <t>The methodology-listed official ACS B25032/B25127 inputs and eight same-vintage annual structure/age/exposure constructions are implemented at county and Census-ZCTA geography; the structural exposure bounds are null before 2020 and are not legal eligibility determinations. Five 2020-2024 annual Los Angeles County sensitivities multiply the exact December county ZORI year-over-year change by the same-ending-year structural lower and upper exposure bounds without monthly carry-forward. These are not observed rent growth inside legally noncontrolled units. Exact noncontrolled_exposure_share and exact exposure-adjusted growth remain unavailable until a complete dated property-level policy/exemption crosswalk exists. The official-source scaffold is not applied, and Census ZCTAs are not USPS postal ZIPs.</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -2560,17 +2608,17 @@
         <v>1</v>
       </c>
       <c r="Y8" s="1" t="n">
-        <v>42035</v>
+        <v>44196</v>
       </c>
       <c r="Z8" s="1" t="n">
-        <v>46173</v>
+        <v>45657</v>
       </c>
       <c r="AA8" t="n">
-        <v>33702</v>
+        <v>2760</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15699 missing of 33702 fact rows</t>
+          <t>0 missing of 2760 panel cells</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -2606,12 +2654,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Eviction Lab ETS where available; otherwise annual filings with interpolation.</t>
+          <t>Use Eviction Lab ETS only where the official release contains the geography; otherwise retain official annual modeled estimates at native annual frequency without interpolation.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Partially implemented</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2636,12 +2684,12 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>modeled</t>
+          <t>modeled annual</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Eviction Lab ETS does not cover Los Angeles County, and the official observed/validated county analysis files do not contain LA County rows. The implemented source is the official Eviction Lab annual county modeled estimates for 2000-2018, with source observation flags and 95% credible interval bounds preserved. Do not treat as monthly/high-frequency ETS or direct local court filings.</t>
+          <t>The official ETS Version 3.0 release was checked on 2026-08-16 and contains neither Los Angeles nor any California geography; the official observed/validated county analysis files also contain no LA County rows. The implementation therefore retains official Eviction Lab annual county modeled estimates for 2000-2018, with source-observation flags and 95% credible interval bounds preserved. No annual value is interpolated or expanded to monthly frequency, and the series is not direct local court filing data.</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
@@ -2676,7 +2724,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ready for data-collection use</t>
+          <t>Review documented limitation before modeling</t>
         </is>
       </c>
     </row>
@@ -2707,42 +2755,42 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Proxy with lagged multifamily permits (5+) using completion lag structure; lags uncertain.</t>
+          <t>Use separately labeled Central and Slow distributed-lag scenarios from 5+ unit permits, with the approved bucket weights and complete-lag missingness rules.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Proxy input only</t>
+          <t>Proxy implemented</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>census_bps_county|census_bps_state</t>
+          <t>census_bps_county</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>permits_5_plus_units</t>
+          <t>new_apartments_completed_proxy_central|new_apartments_completed_proxy_slow</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>analytics.fact_housing_observation|analytics.county_monthly_panel</t>
+          <t>analytics.county_monthly_panel|analytics.renter_market_monthly</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>permits_5_plus_units</t>
+          <t>new_apartments_completed_proxy_central|new_apartments_completed_proxy_slow</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>proxy input</t>
+          <t>modeled Central and Slow scenarios</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>The sheet workaround is lagged multifamily permits with an explicit completion-lag structure; permits are loaded, but no completion proxy is calculated.</t>
+          <t>Central distributes 20% of each 5+ permit cohort equally over lags 12-17, 55% over lags 18-23, and 25% over lags 24-30; Slow distributes 20% over lags 18-23, 50% over lags 24-29, and 30% over lags 30-36. Central has 288 and Slow 282 non-null LA County months. Every required lag must be present, missing permits are never zero-filled, and there is no unsuffixed best estimate. These are panel-derived scenario fields exposed in the county panel and renter view; they are intentionally not materialized as native rows in analytics.fact_housing_observation.</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
@@ -2756,28 +2804,28 @@
         <v>1</v>
       </c>
       <c r="W10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X10" t="b">
         <v>1</v>
       </c>
       <c r="Y10" s="1" t="n">
-        <v>36556</v>
+        <v>37468</v>
       </c>
       <c r="Z10" s="1" t="n">
-        <v>46173</v>
+        <v>46265</v>
       </c>
       <c r="AA10" t="n">
-        <v>634</v>
+        <v>574</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0 missing of 634 fact rows</t>
+          <t>0 missing of 574 panel cells</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Review documented limitation before modeling</t>
+          <t>Ready for data-collection use</t>
         </is>
       </c>
     </row>
@@ -2808,42 +2856,42 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Build pipeline stock: cumulative MF permits minus assumed completions over rolling window.</t>
+          <t>Build separately labeled Central and Slow stock-flow scenarios from current permits, scenario completions, and every surviving pre-output permit cohort; never initialize the opening stock to zero.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Proxy input only</t>
+          <t>Proxy implemented</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>census_bps_county|census_bps_state</t>
+          <t>census_bps_county</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>permits_5_plus_units</t>
+          <t>multifamily_under_construction_proxy_central|multifamily_under_construction_proxy_slow</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>analytics.fact_housing_observation|analytics.county_monthly_panel</t>
+          <t>analytics.county_monthly_panel|analytics.renter_market_monthly</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>permits_5_plus_units</t>
+          <t>multifamily_under_construction_proxy_central|multifamily_under_construction_proxy_slow</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>proxy input</t>
+          <t>modeled Central and Slow scenarios</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>The sheet workaround is cumulative MF permits minus assumed completions over a rolling window; permit inputs are loaded, but the stock pipeline calculation is not implemented.</t>
+          <t>Each scenario follows prior stock + current 5+ permits - scenario completions. Opening stock includes every permit cohort with positive uncompleted weight in a complete 30-month Central or 36-month Slow active window rather than starting at zero. Central has 289 and Slow 283 non-null LA County months; missing active-window inputs propagate to null and no unsuffixed best estimate is emitted. These are panel-derived scenario fields exposed in the county panel and renter view; they are intentionally not materialized as native rows in analytics.fact_housing_observation.</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
@@ -2857,28 +2905,28 @@
         <v>1</v>
       </c>
       <c r="W11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X11" t="b">
         <v>1</v>
       </c>
       <c r="Y11" s="1" t="n">
-        <v>36556</v>
+        <v>37437</v>
       </c>
       <c r="Z11" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="AA11" t="n">
-        <v>634</v>
+        <v>572</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0 missing of 634 fact rows</t>
+          <t>0 missing of 572 panel cells</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Review documented limitation before modeling</t>
+          <t>Ready for data-collection use</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2962,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Proxy input only</t>
+          <t>Not implemented</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -2932,19 +2980,15 @@
           <t>analytics.fact_housing_observation|analytics.county_monthly_panel</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>permits_1_unit</t>
-        </is>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>proxy input</t>
+          <t>closed / not pursued</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>The sheet workaround needs SFR permits combined with investor/rental-growth tract logic; only 1-unit permits are loaded.</t>
+          <t>The approved decision keeps this target closed. Generic one-unit permits do not identify rental tenure or investor intent, and the repository does not invent an investor/rental-growth tract classifier. Reopen only if a qualifying official public source and explicit method are approved.</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
@@ -2967,14 +3011,14 @@
         <v>36556</v>
       </c>
       <c r="Z12" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="AA12" t="n">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0 missing of 634 fact rows</t>
+          <t>0 missing of 636 fact rows</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -3025,27 +3069,27 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>acs_renter_occupied_units</t>
+          <t>net_change_occupied_apartments_annual|zcta_renter_occupied_units_vintage_change_annual</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>analytics.county_annual_controls|analytics.fact_housing_observation</t>
+          <t>analytics.county_annual_controls|analytics.zcta_annual_controls</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>acs_renter_occupied_units</t>
+          <t>net_change_occupied_apartments_annual</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>observed</t>
+          <t>proxy</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>ACS annual 5-year renter-occupied units are available; quarterly net change is not created.</t>
+          <t>Fourteen consecutive-vintage annual county differences are implemented for 2011-2024, and 3,562 exact-ZCTA differences are implemented for 2012-2024. Both are panel-only constructions from direct acs_renter_occupied_units inputs and are not fact observations. Adjacent ACS five-year estimates overlap for four survey years, so neither result is a one-year flow; no quarterly timing is created, and Census ZCTAs are not postal ZIPs.</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
@@ -3056,26 +3100,26 @@
         <v>1</v>
       </c>
       <c r="V13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X13" t="b">
         <v>1</v>
       </c>
       <c r="Y13" s="1" t="n">
-        <v>45657</v>
+        <v>40908</v>
       </c>
       <c r="Z13" s="1" t="n">
         <v>45657</v>
       </c>
       <c r="AA13" t="n">
-        <v>275</v>
+        <v>14</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>0 missing of 275 fact rows</t>
+          <t>0 missing of 14 panel cells</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -3126,19 +3170,19 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
+          <t>county_annual_price_to_income_acs|zcta_annual_price_to_income_acs</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>analytics.county_annual_controls|analytics.zcta_annual_controls</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
           <t>county_annual_price_to_income_acs</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>analytics.county_annual_controls</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>county_annual_price_to_income_acs</t>
-        </is>
-      </c>
       <c r="O14" t="inlineStr">
         <is>
           <t>constructed</t>
@@ -3146,7 +3190,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Annual ACS ratio is implemented; quarterly/local alternatives are deferred.</t>
+          <t>Fifteen annual LA County ACS ratios are implemented for 2010-2024. Matched-vintage ratios are also implemented for the 274 configured Census ZCTAs for 2011-2024, with six source-null ZCTA-vintages preserved and 3,830 non-null ratios. Both ratios are panel-only constructions rather than fact observations. No quarterly timing is invented, and Census ZCTAs are not postal ZIPs.</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr"/>
@@ -3157,7 +3201,7 @@
         <v>1</v>
       </c>
       <c r="V14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="b">
         <v>0</v>
@@ -3165,12 +3209,20 @@
       <c r="X14" t="b">
         <v>1</v>
       </c>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
+      <c r="Y14" s="1" t="n">
+        <v>40543</v>
+      </c>
+      <c r="Z14" s="1" t="n">
+        <v>45657</v>
+      </c>
       <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>0 missing of 15 panel cells</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr">
         <is>
           <t>Review documented limitation before modeling</t>
@@ -3315,32 +3367,32 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>irs_soi_county_migration</t>
+          <t>irs_soi_county_migration|census_pep_county_population_v2019|census_pep_county_population_v2025|census_acs_5year_b05002|census_acs_5year_b07001</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>irs_soi_net_migration_exemptions|irs_soi_net_migration_returns|irs_soi_net_migration_agi</t>
+          <t>irs_soi_net_migration_exemptions|irs_soi_net_migration_returns|irs_soi_net_migration_agi|census_pep_county_population_annual|net_exemption_rate|acs_foreign_born_population|acs_foreign_born_population_moe|acs_moved_from_abroad_past_year|acs_moved_from_abroad_past_year_moe</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>analytics.county_annual_controls|analytics.fact_housing_observation</t>
+          <t>analytics.county_annual_controls|analytics.zcta_annual_controls|analytics.fact_housing_observation</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>irs_soi_net_migration_exemptions</t>
+          <t>irs_soi_net_migration_exemptions|census_pep_county_population_annual|net_exemption_rate|acs_foreign_born_population|acs_moved_from_abroad_past_year</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>constructed</t>
+          <t>constructed IRS net values|observed ACS survey supplements</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Annual IRS SOI in-migration minus out-migration is implemented. Exemptions approximate people and are the preferred public proxy; returns approximate tax filing units; AGI captures income composition. This is migration based on tax return address changes, not complete immigration.</t>
+          <t>Annual IRS SOI in-migration minus out-migration is implemented, with exemptions as the preferred tax-return people proxy and returns/AGI retained as companions. net_exemption_rate divides each interval's net exemptions by official Census PEP resident population for that same ending year and multiplies by 1,000; it never uses prior-year or ACS population and remains annual. The methodology recommends ACS foreign-born and residence-one-year-ago county supplements and lists the Census ACS source family; after user approval, those concepts are operationalized with official B05002 and B07001. The foreign-born field is a population stock and the moved-from-abroad field is gross current-resident mobility; both remain separate annual five-year survey estimates with their published 90-percent margins of error. Neither is net migration or a replacement for IRS SOI; five-year vintages overlap and are not expanded to monthly frequency. Census-ZCTA rows are a separately labeled repository extension, never postal ZIPs. The IRS 2022-2023 interval remains explicitly flagged as the provider's enhanced-matching/new-series methodology break.</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr"/>
@@ -3360,17 +3412,17 @@
         <v>1</v>
       </c>
       <c r="Y16" s="1" t="n">
-        <v>40908</v>
+        <v>40543</v>
       </c>
       <c r="Z16" s="1" t="n">
-        <v>45291</v>
+        <v>46022</v>
       </c>
       <c r="AA16" t="n">
-        <v>39</v>
+        <v>15459</v>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>0 missing of 39 fact rows</t>
+          <t>0 missing of 15459 fact rows</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -3411,21 +3463,37 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Not implemented</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>Partially implemented</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>hud_pit_coc_2007_2025</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hud_pit_overall_homeless_annual|hud_pit_sheltered_homeless_annual|hud_pit_unsheltered_homeless_annual</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>analytics.fact_housing_observation|analytics.coc_annual_controls</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>hud_pit_overall_homeless_annual|hud_pit_sheltered_homeless_annual|hud_pit_unsheltered_homeless_annual</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>deferred</t>
+          <t>observed annual control</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>The sheet workaround specifies annual HUD PIT; HUD PIT/CoC data is not loaded.</t>
+          <t>The official HUD PIT annual 2007-2025 CoC source and explicit CA-600/606/607/612 project composite are implemented. The source is annual point-in-time only, the composite is not Los Angeles County, and row-level sheltered-only, partial-unsheltered, and no-count records remain analytically incomplete. Explicit geography-year rows remain in CoC annual controls even when all three analytical values are null; the requested high-frequency target is still unavailable.</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr"/>
@@ -3433,23 +3501,31 @@
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" t="b">
         <v>0</v>
       </c>
       <c r="W17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X17" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Y17" s="1" t="n">
+        <v>39447</v>
+      </c>
+      <c r="Z17" s="1" t="n">
+        <v>46022</v>
+      </c>
       <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="inlineStr"/>
+        <v>22350</v>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>1742 missing of 22350 fact rows</t>
+        </is>
+      </c>
       <c r="AC17" t="inlineStr">
         <is>
           <t>Review documented limitation before modeling</t>
@@ -3653,11 +3729,11 @@
         <v>46173</v>
       </c>
       <c r="AA19" t="n">
-        <v>23182</v>
+        <v>24391</v>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>63 missing of 23182 fact rows</t>
+          <t>63 missing of 24391 fact rows</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3758,11 +3834,11 @@
         <v>46173</v>
       </c>
       <c r="AA20" t="n">
-        <v>173</v>
+        <v>1382</v>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>0 missing of 173 fact rows</t>
+          <t>0 missing of 1382 fact rows</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3863,11 +3939,11 @@
         <v>46173</v>
       </c>
       <c r="AA21" t="n">
-        <v>173</v>
+        <v>1382</v>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0 missing of 173 fact rows</t>
+          <t>0 missing of 1382 fact rows</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3968,11 +4044,11 @@
         <v>46173</v>
       </c>
       <c r="AA22" t="n">
-        <v>23182</v>
+        <v>24391</v>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>31 missing of 23182 fact rows</t>
+          <t>31 missing of 24391 fact rows</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -4073,11 +4149,11 @@
         <v>46173</v>
       </c>
       <c r="AA23" t="n">
-        <v>23182</v>
+        <v>24391</v>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>63 missing of 23182 fact rows</t>
+          <t>63 missing of 24391 fact rows</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -4232,32 +4308,32 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>census_bps_county|census_bps_state</t>
+          <t>census_bps_county|census_bps_state|census_bps_county_annual_final|census_pep_county_housing_units_v2019|census_pep_county_housing_units_v2025</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>permits_1_unit</t>
+          <t>permits_1_unit|permits_1_unit_annual_final|census_pep_county_housing_units_annual|permits_1_unit_per_1000_housing_units</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>analytics.fact_housing_observation|analytics.county_monthly_panel</t>
+          <t>analytics.fact_housing_observation|analytics.county_monthly_panel|analytics.county_annual_controls</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>permits_1_unit</t>
+          <t>permits_1_unit|permits_1_unit_per_1000_housing_units</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>proxy</t>
+          <t>authorization proxy|constructed annual rate</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Census BPS permits are authorizations, not starts or completions.</t>
+          <t>Census BPS permits are authorizations, not starts or completions. The annual normalized rate divides final annual one-unit permits by the same-year Census PEP July 1 housing-unit estimate and multiplies by 1,000. It is retained annually and never constructed from monthly permits or an ACS/lagged denominator.</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr"/>
@@ -4277,17 +4353,17 @@
         <v>1</v>
       </c>
       <c r="Y25" s="1" t="n">
-        <v>36556</v>
+        <v>33238</v>
       </c>
       <c r="Z25" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="AA25" t="n">
-        <v>634</v>
+        <v>688</v>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0 missing of 634 fact rows</t>
+          <t>0 missing of 688 fact rows</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -4389,14 +4465,14 @@
         <v>42035</v>
       </c>
       <c r="Z26" s="1" t="n">
-        <v>46173</v>
+        <v>46265</v>
       </c>
       <c r="AA26" t="n">
-        <v>33702</v>
+        <v>36960</v>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15699 missing of 33702 fact rows</t>
+          <t>17221 missing of 36960 fact rows</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4490,12 +4566,20 @@
       <c r="X27" t="b">
         <v>1</v>
       </c>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
+      <c r="Y27" s="1" t="n">
+        <v>42063</v>
+      </c>
+      <c r="Z27" s="1" t="n">
+        <v>46265</v>
+      </c>
       <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="inlineStr"/>
+        <v>267</v>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>0 missing of 267 panel cells</t>
+        </is>
+      </c>
       <c r="AC27" t="inlineStr">
         <is>
           <t>Ready for data-collection use</t>
@@ -4542,37 +4626,21 @@
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Partially implemented – ACS annual availability and HUD/USPS quarterly proxies; monthly listings unavailable</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>census_acs_5year_b25003|census_acs_5year_b25004|hud_usps_ncwm_quarterly</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>acs_renter_occupied_units|acs_renter_occupied_units_moe|acs_for_rent_vacant_units|acs_for_rent_vacant_units_moe|acs_rental_availability_rate|usps_total_residential_addresses|usps_short_term_vacant_residential_addresses|usps_long_term_vacant_residential_addresses|usps_vacant_residential_addresses|usps_no_stat_residential_addresses|usps_active_residential_addresses|usps_residential_vacancy_rate|usps_residential_no_stat_rate</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>analytics.fact_housing_observation|analytics.county_annual_controls|data/restricted/hud_usps/active/ca_county_quarterly.parquet|data/restricted/hud_usps/active/la_tract_2020_quarterly.parquet|data/restricted/hud_usps/active/la_postal_zip_county_part_quarterly.parquet|data/restricted/hud_usps/active/long_observations_with_lineage.parquet</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>acs_renter_occupied_units|acs_renter_occupied_units_moe|acs_for_rent_vacant_units|acs_for_rent_vacant_units_moe|acs_rental_availability_rate|usps_total_residential_addresses|usps_short_term_vacant_residential_addresses|usps_long_term_vacant_residential_addresses|usps_vacant_residential_addresses|usps_no_stat_residential_addresses|usps_active_residential_addresses|usps_residential_vacancy_rate|usps_residential_no_stat_rate</t>
-        </is>
-      </c>
+          <t>Not implemented</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
-          <t>separate annual and quarterly proxies</t>
+          <t>unavailable target</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>The annual ACS rental-availability proxy is for-rent vacant units divided by renter-occupied plus for-rent vacant units, using matched B25003 and B25004 estimates. Component 90% margins of error are retained, and unreliable county ratios are suppressed. Direct ACS counts and margins of error are retained at county and ZCTA geography; ZCTAs are not postal ZIPs. The eight active HUD-USPS variables are native-quarterly only and remain a separate all-residential measure. The vacancy proxy is (short-term vacant + long-term vacant) / total residential addresses, while no-stat remains a separate diagnostic. Direct provider components are observed at standardized 2020-tract geography; California county aggregates are constructed, and Los Angeles County postal-ZIP county-parts are modeled with the fixed 2026 Q1 crosswalk. Detailed tract and modeled ZIP-part derivatives remain access-controlled under the HUD-USPS sublicense. This is not true rental-listing inventory; ZORI is not inventory (it is a rent index), and Redfin for-sale active listings are not a valid substitute. The monthly rental-listing series remains missing at documented source and license acquisition. The former derived package file was deleted; its historical quarantine manifest is superseded and is not an active input.</t>
+          <t>The annual ACS rental-availability proxy is for-rent vacant units divided by renter-occupied plus for-rent vacant units, using matched B25003 and B25004 estimates. Component 90% margins of error are retained, and unreliable county ratios are suppressed. Direct ACS counts and margins of error are retained at county and ZCTA geography; ZCTAs are not postal ZIPs. The eight active HUD-USPS variables are native-quarterly only and remain a separate all-residential measure. The vacancy proxy is (short-term vacant + long-term vacant) / total residential addresses, while no-stat remains a separate diagnostic. Direct provider components are observed at standardized 2020-tract geography; California county aggregates are constructed, and Los Angeles County postal-ZIP county-parts are modeled with the fixed 2026 Q1 crosswalk. Detailed tract and modeled ZIP-part derivatives remain access-controlled under the HUD-USPS sublicense. This is not true rental-listing inventory; ZORI is not inventory (it is a rent index), and Redfin for-sale active listings are not a valid substitute. The governing methodology names no approved source for the true monthly rental-listing series, so the blocker is a methodology/source-identification decision rather than a credential or coding step. The former derived package file was deleted; its historical quarantine manifest is superseded and is not an active input.</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr"/>
@@ -4580,31 +4648,23 @@
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X28" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y28" s="1" t="n">
-        <v>39538</v>
-      </c>
-      <c r="Z28" s="1" t="n">
-        <v>46112</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="n">
-        <v>1770036</v>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>9256 missing of 1770036 fact rows</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr">
         <is>
           <t>Review documented limitation before modeling</t>
@@ -4813,14 +4873,14 @@
         <v>36556</v>
       </c>
       <c r="Z30" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="AA30" t="n">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>0 missing of 634 fact rows</t>
+          <t>0 missing of 636 fact rows</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4865,27 +4925,27 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Partially implemented - alternate source</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>zillow_county_zhvi|zillow_county_zori_smoothed_sa</t>
+          <t>zillow_county_zhvi|zillow_zip_zhvi|zillow_county_zori_smoothed_sa|zillow_zip_zori_smoothed_sa</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>price_to_rent_ratio</t>
+          <t>price_to_rent_ratio_zillow|price_to_rent_ratio|implied_gross_rent_yield</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>analytics.county_monthly_panel</t>
+          <t>analytics.county_monthly_panel|analytics.zip_monthly_panel</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>price_to_rent_ratio</t>
+          <t>price_to_rent_ratio_zillow|implied_gross_rent_yield</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -4895,7 +4955,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>The active monthly panel ratio uses ZHVI/ZORI. The sheet specifies FHFA/ZORI; that version needs an explicit FHFA index-to-rent construction choice and is not yet implemented.</t>
+          <t>The latest methodology governs: matched-month positive Zillow ZHVI divided by active smoothed-seasonally-adjusted ZORI is the canonical county and postal-ZIP ratio. The inverse gross-yield measure remains explicitly labeled gross.</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr"/>
@@ -4914,15 +4974,23 @@
       <c r="X31" t="b">
         <v>1</v>
       </c>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
+      <c r="Y31" s="1" t="n">
+        <v>42035</v>
+      </c>
+      <c r="Z31" s="1" t="n">
+        <v>46265</v>
+      </c>
       <c r="AA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="inlineStr"/>
+        <v>37526</v>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>0 missing of 37526 panel cells</t>
+        </is>
+      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Review documented limitation before modeling</t>
+          <t>Ready for data-collection use</t>
         </is>
       </c>
     </row>
@@ -4962,7 +5030,7 @@
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Partially implemented</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4992,7 +5060,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sales/inventory liquidity is implemented; sales/housing-stock turnover is deferred.</t>
+          <t>The listed Redfin sales-to-inventory and inventory-to-sales liquidity proxies are implemented. They are not true sales divided by total housing stock and retain that qualification.</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr"/>
@@ -5011,15 +5079,23 @@
       <c r="X32" t="b">
         <v>1</v>
       </c>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
+      <c r="Y32" s="1" t="n">
+        <v>40939</v>
+      </c>
+      <c r="Z32" s="1" t="n">
+        <v>46173</v>
+      </c>
       <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="inlineStr"/>
+        <v>346</v>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>0 missing of 346 panel cells</t>
+        </is>
+      </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Review documented limitation before modeling</t>
+          <t>Ready for data-collection use</t>
         </is>
       </c>
     </row>
@@ -5115,11 +5191,11 @@
         <v>46173</v>
       </c>
       <c r="AA33" t="n">
-        <v>23182</v>
+        <v>24391</v>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>63 missing of 23182 fact rows</t>
+          <t>63 missing of 24391 fact rows</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -5220,11 +5296,11 @@
         <v>46173</v>
       </c>
       <c r="AA34" t="n">
-        <v>173</v>
+        <v>1382</v>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>1 missing of 173 fact rows</t>
+          <t>2 missing of 1382 fact rows</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5435,14 +5511,14 @@
         <v>32904</v>
       </c>
       <c r="Z36" s="1" t="n">
-        <v>46173</v>
+        <v>46265</v>
       </c>
       <c r="AA36" t="n">
-        <v>437</v>
+        <v>3513</v>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>1 missing of 437 fact rows</t>
+          <t>8 missing of 3513 fact rows</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5540,14 +5616,14 @@
         <v>32904</v>
       </c>
       <c r="Z37" s="1" t="n">
-        <v>46173</v>
+        <v>46265</v>
       </c>
       <c r="AA37" t="n">
-        <v>1311</v>
+        <v>10539</v>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>3 missing of 1311 fact rows</t>
+          <t>24 missing of 10539 fact rows</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -5596,7 +5672,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Partially implemented</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -5626,7 +5702,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Aligned with BEA as the sheet source. State quarterly is loaded; county is annual because county quarterly personal income is limited/noisier as noted in the sheet.</t>
+          <t>Aligned with BEA as the listed source. California quarterly and Los Angeles County annual series are loaded at their native frequencies; the county annual values are never relabeled as observed quarterly data.</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr"/>
@@ -5661,7 +5737,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Review documented limitation before modeling</t>
+          <t>Ready for data-collection use</t>
         </is>
       </c>
     </row>
@@ -5785,7 +5861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5887,27 +5963,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>acs_rental_availability_proxy_v1</t>
+          <t>sipp_ca_primary_residence_debt_sensitivity_v1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>acs_rental_availability_rate</t>
+          <t>sipp_ca_aggregate_primary_residence_debt_sensitivity</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Matched annual ACS rental-availability proxy</t>
+          <t>Published-table state sensitivity formula</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>For the 2024 ACS five-year vintage, B25004 for-rent vacant units / (B25003 renter-occupied units + B25004 for-rent vacant units). Both component 90% margins of error are retained; the rate is suppressed when either component MOE is greater than or equal to its estimate. The annual value is not interpolated or expanded to monthly frequency.</t>
+          <t>California households (14,420 thousand) * published Home Debt holding share (32.6 percent) * published conditional mean Home Debt ($346,200) = $1,627,458,504,000 for 2024.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>This preserves a transparent annual rental-availability proxy with matched ACS universes and explicit reliability screening. It is not an active rental-listing stock, and it remains separate from the quarterly HUD-USPS all-residential proxy.</t>
+          <t>This 2025 SIPP public table product is separately labeled because the inputs are rounded, the conditional mean is limited to households with total debt below the 99th percentile, and Home Debt is broader than the exact owner-occupied closed-end first-lien calibration universe. No county allocation or covariance-based aggregate standard error is created.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -5919,27 +5995,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hud_usps_residential_vacancy_proxy_v2</t>
+          <t>sipp_ca_positive_home_equity_sensitivity_v1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>usps_residential_vacancy_rate</t>
+          <t>sipp_ca_aggregate_positive_home_equity_sensitivity</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>All-residential vacancy-proxy formula</t>
+          <t>Published-table state sensitivity formula</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>(short-term vacant residential addresses + long-term vacant residential addresses) / total residential addresses; rates remain ratios in [0, 1].</t>
+          <t>California households (14,420 thousand) * published Equity in Own Home holding share (51.0 percent) * published conditional mean Equity in Own Home ($668,100) = $4,913,341,020,000 for 2024.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>No-stat residential addresses remain a separate count and rate diagnostic and never enter the vacancy numerator. This is an all-residential address-status proxy, not rental-listing inventory.</t>
+          <t>This 2025 SIPP public table product is separately labeled because it covers positive-equity holders, uses rounded inputs, and the conditional mean is limited to households with net worth below the 99th percentile. It is not a matched-universe county equity benchmark, and no covariance-based aggregate standard error is created.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -5951,27 +6027,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hud_usps_residential_vacancy_proxy_v2</t>
+          <t>ahs_table14a_reported_case_outstanding_principal_proxy_v1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>usps_residential_vacancy_rate</t>
+          <t>ahs_ca_reported_case_primary_mortgage_outstanding_principal_proxy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Official active provenance</t>
+          <t>AHS reported-case public calibration proxy</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>provenance_status=official_raw_archive_rebuilt; 75 immutable official artifacts are indexed by metadata/hud_usps_source_manifest.csv, including 73 contiguous 2008 Q1-2026 Q1 NCWM responses, the 2026 Q1 tract-to-postal-ZIP crosswalk, and the 2020 Census California county reference.</t>
+          <t>Sum of fourteen published 2023 California reported outstanding-principal-bin household estimates (3,381.2 thousand) * 1,000 * published conditional mean outstanding principal ($418,100) = $1,413,679,720,000.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Every active observation is rebuilt from the verified official archive. The former derived package file was deleted; only its historical, superseded quarantine manifest remains, and it is not an active input.</t>
+          <t>The Four Variable Data Status Report authorizes AHS as the primary public proxy. The construction excludes 1,203.8 thousand regular-mortgage households with unreported balances, does not assign them the reported-case mean, and emits no all-household extrapolation or covariance-based aggregate uncertainty. AHS primary mortgage may not equal legal first lien, and the 2023 statewide proxy does not silently populate county targets calibrated to the current Version A universe and 2022-07-01 reference date.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -5983,27 +6059,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>hud_usps_residential_vacancy_proxy_v2</t>
+          <t>acs_rental_availability_proxy_v1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>usps_residential_vacancy_rate</t>
+          <t>acs_rental_availability_rate</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Geography-specific construction</t>
+          <t>Matched annual ACS rental-availability proxy</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Provider component fields are direct at standardized 2020-tract geography; California county values are constructed from complete tract components; Los Angeles County postal-ZIP county-part values are modeled with the fixed 2026 Q1 crosswalk.</t>
+          <t>For each matched 2010-2024 ACS five-year county vintage, B25004 for-rent vacant units / (B25003 renter-occupied units + B25004 for-rent vacant units). Both component 90% margins of error are retained; the rate is suppressed when either component MOE is greater than or equal to its estimate. Annual values are not interpolated or expanded to monthly frequency.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Modeled ZIP rows describe only the Los Angeles County portion of USPS postal ZIPs. They are neither whole postal ZIPs nor Census ZCTAs, and no tract percentages are averaged.</t>
+          <t>This preserves a transparent annual rental-availability proxy with matched ACS universes and explicit reliability screening. It is not an active rental-listing stock, and it remains separate from the quarterly HUD-USPS all-residential proxy.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -6015,27 +6091,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>hud_usps_residential_vacancy_proxy_v2</t>
+          <t>acs_noncontrolled_structural_exposure_bounds_v1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>usps_residential_no_stat_rate</t>
+          <t>acs_renter_occupied_1_unit_share|acs_renter_occupied_2_to_4_units_share|acs_renter_occupied_5_plus_units_share|acs_renter_occupied_mobile_other_share</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Quarterly-only restricted diagnostic</t>
+          <t>Same-vintage B25032 renter structure shares</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>No-stat / total remains a separate native-quarterly diagnostic. The eight active variables are stored in the common fact and restricted native-quarterly tables; they are not expanded into observed months.</t>
+          <t>Divide the mutually exclusive B25032 renter-occupied structure groups by the same-vintage B25032 renter total. Combine detached and attached for one unit; combine two and three-to-four for two-to-four; combine all published five-plus cells; combine mobile home and boat-RV-other.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Licensed tract and modeled postal-ZIP county-part observations and derivatives remain access-controlled under data/restricted/hud_usps/ and outside public exports under the HUD-USPS sublicense.</t>
+          <t>These are transparent annual descriptive structure shares at county or Census-ZCTA geography. They do not by themselves classify rent-control coverage, and they are never interpolated or expanded to months.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -6047,283 +6123,283 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>acs_implied_mortgage_debt_proxy_legacy_v0</t>
+          <t>acs_noncontrolled_structural_exposure_bounds_v1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>acs_implied_aggregate_mortgage_debt_proxy</t>
+          <t>acs_renter_recent_construction_share_lower_bound|acs_renter_recent_construction_share_upper_bound</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Legacy ACS B25106 table role</t>
+          <t>Vintage-normalized B25127 recent-construction bounds</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Legacy scenario only: B25106 owner income x housing-cost-burden bins infer monthly owner housing costs; B25106 is not an observed mortgage balance and is not the authoritative Version A method.</t>
+          <t>Lower = normalized definitely-recent renter total / B25127 renter total. Upper = (definitely-recent renter total + cutoff-mixed renter total) / B25127 renter total. Regimes are 2000+ and 1980-1999 for 2010-2014; 2010+ and 2000-2009 for 2015-2020; and 2020+ and 2000-2019 for 2021-2024.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Retained in facts for reproducibility and labeled legacy; do not select it in place of the Version A _benchmark variables.</t>
+          <t>Published B25127 year-built bins and cell sequences change across vintages and cannot recover an exact rolling 15-year cutoff. Resolving cells by label and retaining a lower/upper interval prevents false precision.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>legacy</t>
+          <t>active</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>acs_implied_mortgage_debt_proxy_legacy_v0</t>
+          <t>acs_noncontrolled_structural_exposure_bounds_v1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>acs_implied_aggregate_mortgage_debt_proxy</t>
+          <t>noncontrolled_exposure_share_structural_proxy_lower_bound</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Income bin midpoints</t>
+          <t>2020 publication floor and lower structural proxy</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10000; 27500; 42500; 62500; 112500</t>
+          <t>For ACS observations ending in 2020 or later, publish normalized B25127 definitely-recent renter total / B25127 renter total; preserve null before 2020.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Closed bins use midpoint values. The open-ended $75k+ bin uses $112,500, or 1.5 times the lower bound, as a transparent conservative top-bin assumption.</t>
+          <t>The 2020 floor corresponds to the AB 1482 effective period but is not proof that any unit is legally exempt or noncontrolled.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>legacy</t>
+          <t>active</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>acs_implied_mortgage_debt_proxy_legacy_v0</t>
+          <t>acs_noncontrolled_structural_exposure_bounds_v1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>acs_implied_aggregate_mortgage_debt_proxy</t>
+          <t>noncontrolled_exposure_share_structural_proxy_upper_bound</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Housing-cost-burden midpoints</t>
+          <t>Broad recent-age and one-unit union upper proxy</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.10 for &lt;20%; 0.25 for 20-29%; 0.40 for 30%+</t>
+          <t>For 2020 onward, min(1, (B25127 definitely-recent total + B25127 cutoff-mixed total + B25032 one-unit total - B25127 definitely-recent one-unit - B25127 cutoff-mixed one-unit) / B25127 renter total).</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Closed or semi-closed categories use practical midpoints; 30%+ uses 40% to avoid implying unlimited burden while retaining high-burden signal.</t>
+          <t>Subtracting the two B25127 one-unit components prevents double counting. Treating every remaining one-unit rental as potentially exempt makes this deliberately broad because ACS does not observe ownership and tenant-notice conditions.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>legacy</t>
+          <t>active</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>acs_implied_mortgage_debt_proxy_legacy_v0</t>
+          <t>acs_noncontrolled_structural_exposure_bounds_v1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>acs_implied_aggregate_mortgage_debt_proxy</t>
+          <t>noncontrolled_exposure_share</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Debt-service share of ACS owner housing cost</t>
+          <t>Exact point estimate remains absent</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>config/rent_control_policy_crosswalk.csv is an official-source scaffold marked scaffold_only_not_applied. It is incomplete across incorporated municipalities and has no property-level join to the annual ACS aggregates.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ACS owner housing costs include non-debt items such as taxes, insurance, utilities, and fees; 80% assigns most but not all inferred owner cost to mortgage debt service.</t>
+          <t>A defensible point estimate requires dated state and local rules, jurisdiction, property age, ownership and notice status, affordable-housing and other exemptions, plus an approved aggregation rule. COUNTY_06037 cannot represent an unincorporated-only ordinance, and Census ZCTAs are not USPS postal ZIPs.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>legacy</t>
+          <t>blocked</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>acs_implied_mortgage_debt_proxy_legacy_v0</t>
+          <t>acs_renter_occupied_vintage_change_v1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>acs_implied_aggregate_mortgage_debt_proxy</t>
+          <t>net_change_occupied_apartments_annual</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mortgage-rate assumption</t>
+          <t>Consecutive ACS vintage difference</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Mean Freddie Mac PMMS monthly-average 30-year fixed rate over the ACS five-year estimate window.</t>
+          <t>Subtract the immediately prior ending-year B25003 renter-occupied estimate only when both county vintages exist and their ending years are consecutive. Do not allocate or forward-fill the result to quarters.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>The ACS 5-year estimate pools observations over five years; using the same window avoids using only one endpoint-year rate.</t>
+          <t>Adjacent ACS five-year estimates overlap for four survey years. The result is a transparent vintage-to-vintage change proxy, not an observed one-year or quarterly flow.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>legacy</t>
+          <t>active</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>acs_implied_mortgage_debt_proxy_legacy_v0</t>
+          <t>acs_county_price_to_income_v1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>acs_implied_aggregate_mortgage_debt_proxy</t>
+          <t>county_annual_price_to_income_acs</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remaining amortization term</t>
+          <t>Matched-vintage Los Angeles County price-to-income ratio</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>25 years</t>
+          <t>For each 2010-2024 ACS ending vintage, divide B25077 median home value by B19013 median household income matched on Los Angeles County and the exact ending year. Preserve a null when either source estimate is null or invalid, and retain the construction only in county annual controls.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Outstanding balances are on existing mortgages, not all new 30-year loans; 25 years is a transparent middle-ground remaining-term assumption.</t>
+          <t>The construction uses matched official ACS five-year facts and does not create a fact observation or monthly/quarterly timing. Structural QA recomputes every eligible ratio from its two panel inputs.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>legacy</t>
+          <t>active</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>acs_implied_mortgage_debt_proxy_legacy_v0</t>
+          <t>acs_zcta_price_to_income_v1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>acs_implied_aggregate_mortgage_debt_proxy</t>
+          <t>zcta_annual_price_to_income_acs</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Allocation of B25081 mortgaged units</t>
+          <t>Matched-vintage Census-ZCTA price-to-income ratio</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>B25081 owner-with-mortgage count is allocated across positive-income B25106 bins proportional to B25106 owner unit counts.</t>
+          <t>For each configured Census ZCTA and 2011-2024 ACS ending vintage, divide B25077 median home value by B19013 median household income from the same ZCTA and vintage. Preserve a null when either source estimate is null or invalid, and do not expand the annual estimate to quarters.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>B25106 bins are not mortgage-status-specific. This forces aggregate mortgaged units to match the directly observed B25081 count while preserving the B25106 income/burden distribution.</t>
+          <t>The construction uses only matched official ACS five-year facts. A Census ZCTA is not a USPS postal ZIP, and published input gaps remain visible rather than being filled.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>legacy</t>
+          <t>active</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>acs_implied_mortgage_debt_proxy_legacy_v0</t>
+          <t>acs_zcta_renter_occupied_vintage_change_v1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>acs_implied_aggregate_mortgage_debt_proxy</t>
+          <t>zcta_renter_occupied_units_vintage_change_annual</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Zero/negative income handling</t>
+          <t>Consecutive ACS B25003 Census-ZCTA vintage difference</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>B25106 zero/negative-income owner units are preserved as an input but excluded from payment-to-balance inference.</t>
+          <t>Within each exact configured Census ZCTA, subtract the immediately prior ending-year B25003 renter-occupied estimate only when both published five-year vintages exist and their ending years are consecutive. Do not allocate, interpolate, or forward-fill the result to quarters.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>A positive income midpoint is required to infer monthly owner housing cost from cost-burden percentages.</t>
+          <t>Adjacent ACS five-year estimates overlap for four survey years. The result is a vintage-to-vintage change, not an observed one-year or quarterly flow, and the Census ZCTA is never relabeled as a postal ZIP.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>legacy</t>
+          <t>active</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>eviction_lab_county_estimates_v1</t>
+          <t>hud_usps_residential_vacancy_proxy_v2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>eviction_lab_filings_estimate_annual</t>
+          <t>usps_residential_vacancy_rate</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LA eviction-source choice</t>
+          <t>All-residential vacancy-proxy formula</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Use official Eviction Lab annual county modeled estimates for Los Angeles County because ETS and the observed/validated county analysis files do not provide LA County rows.</t>
+          <t>(short-term vacant residential addresses + long-term vacant residential addresses) / total residential addresses; rates remain ratios in [0, 1].</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>This preserves the expected Eviction Lab source family without silently substituting another geography, and keeps the limitation explicit for modeling.</t>
+          <t>No-stat residential addresses remain a separate count and rate diagnostic and never enter the vacancy numerator. This is an all-residential address-status proxy, not rental-listing inventory.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -6335,27 +6411,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>eviction_lab_county_rate_v1</t>
+          <t>hud_usps_residential_vacancy_proxy_v2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>eviction_lab_filings_rate_estimate_annual</t>
+          <t>usps_residential_vacancy_rate</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Annual rate denominator</t>
+          <t>Official active provenance</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>filings_estimate divided by Eviction Lab renting_hh, multiplied by 100.</t>
+          <t>provenance_status=official_raw_archive_rebuilt; 75 immutable official artifacts are indexed by metadata/hud_usps_source_manifest.csv, including 73 contiguous 2008 Q1-2026 Q1 NCWM responses, the 2026 Q1 tract-to-postal-ZIP crosswalk, and the 2020 Census California county reference.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>A rate normalizes the trend for renter-household base changes while using only fields published in the same official Eviction Lab file.</t>
+          <t>Every active observation is rebuilt from the verified official archive. The former derived package file was deleted; only its historical, superseded quarantine manifest remains, and it is not an active input.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -6367,30 +6443,702 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>hud_usps_residential_vacancy_proxy_v2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>usps_residential_vacancy_rate</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Geography-specific construction</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Provider component fields are direct at standardized 2020-tract geography; California county values are constructed from complete tract components; Los Angeles County postal-ZIP county-part values are modeled with the fixed 2026 Q1 crosswalk.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Modeled ZIP rows describe only the Los Angeles County portion of USPS postal ZIPs. They are neither whole postal ZIPs nor Census ZCTAs, and no tract percentages are averaged.</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>hud_usps_residential_vacancy_proxy_v2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>usps_residential_no_stat_rate</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Quarterly-only restricted diagnostic</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>No-stat / total remains a separate native-quarterly diagnostic. The eight active variables are stored in the common fact and restricted native-quarterly tables; they are not expanded into observed months.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Licensed tract and modeled postal-ZIP county-part observations and derivatives remain access-controlled under data/restricted/hud_usps/ and outside public exports under the HUD-USPS sublicense.</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>acs_implied_mortgage_debt_proxy_legacy_v0</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>acs_implied_aggregate_mortgage_debt_proxy</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Legacy ACS B25106 table role</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Legacy scenario only: B25106 owner income x housing-cost-burden bins infer monthly owner housing costs; B25106 is not an observed mortgage balance and is not the authoritative Version A method.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Retained in facts for reproducibility and labeled legacy; do not select it in place of the Version A _benchmark variables.</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>acs_implied_mortgage_debt_proxy_legacy_v0</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>acs_implied_aggregate_mortgage_debt_proxy</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Income bin midpoints</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>10000; 27500; 42500; 62500; 112500</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Closed bins use midpoint values. The open-ended $75k+ bin uses $112,500, or 1.5 times the lower bound, as a transparent conservative top-bin assumption.</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>acs_implied_mortgage_debt_proxy_legacy_v0</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>acs_implied_aggregate_mortgage_debt_proxy</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Housing-cost-burden midpoints</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>0.10 for &lt;20%; 0.25 for 20-29%; 0.40 for 30%+</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Closed or semi-closed categories use practical midpoints; 30%+ uses 40% to avoid implying unlimited burden while retaining high-burden signal.</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>acs_implied_mortgage_debt_proxy_legacy_v0</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>acs_implied_aggregate_mortgage_debt_proxy</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Debt-service share of ACS owner housing cost</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>ACS owner housing costs include non-debt items such as taxes, insurance, utilities, and fees; 80% assigns most but not all inferred owner cost to mortgage debt service.</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>acs_implied_mortgage_debt_proxy_legacy_v0</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>acs_implied_aggregate_mortgage_debt_proxy</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Mortgage-rate assumption</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Mean Freddie Mac PMMS monthly-average 30-year fixed rate over the ACS five-year estimate window.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>The ACS 5-year estimate pools observations over five years; using the same window avoids using only one endpoint-year rate.</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>acs_implied_mortgage_debt_proxy_legacy_v0</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>acs_implied_aggregate_mortgage_debt_proxy</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Remaining amortization term</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>25 years</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Outstanding balances are on existing mortgages, not all new 30-year loans; 25 years is a transparent middle-ground remaining-term assumption.</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>acs_implied_mortgage_debt_proxy_legacy_v0</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>acs_implied_aggregate_mortgage_debt_proxy</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Allocation of B25081 mortgaged units</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>B25081 owner-with-mortgage count is allocated across positive-income B25106 bins proportional to B25106 owner unit counts.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>B25106 bins are not mortgage-status-specific. This forces aggregate mortgaged units to match the directly observed B25081 count while preserving the B25106 income/burden distribution.</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>acs_implied_mortgage_debt_proxy_legacy_v0</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>acs_implied_aggregate_mortgage_debt_proxy</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Zero/negative income handling</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>B25106 zero/negative-income owner units are preserved as an input but excluded from payment-to-balance inference.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>A positive income midpoint is required to infer monthly owner housing cost from cost-burden percentages.</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ca_homeowners_premium_real_2023_cpi_v1</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ca_homeowners_avg_written_premium_real</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>California CPI deflator and base year</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>nominal California DOI average written premium in year y multiplied by California DIR annual CPI-U for 2023 and divided by the same annual CPI-U for year y.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>This implements the workbook-approved constant-2023-dollar convention on exact calendar-year matches. The 2023 real value must equal the 2023 nominal value; missing or nonpositive inputs remain null, and no subannual CPI or real-premium observations are fabricated.</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>bps_5_plus_distributed_completion_lag_v1</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>new_apartments_completed_proxy_central</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Central completion timing</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Allocate 20% of each 5+ permit cohort equally across lags 12-17, 55% equally across lags 18-23, and 25% equally across lags 24-30.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>The weights are the exact approved Central scenario and sum to one. All lags 12-30 must be present; a missing source month propagates to a null proxy month rather than being treated as zero.</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>bps_5_plus_distributed_completion_lag_v1</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>new_apartments_completed_proxy_slow</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Slow completion timing</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Allocate 20% of each 5+ permit cohort equally across lags 18-23, 50% equally across lags 24-29, and 30% equally across lags 30-36.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>The weights are the exact approved Slow scenario and sum to one. All lags 18-36 must be present; a missing source month propagates to a null proxy month rather than being treated as zero.</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>bps_5_plus_stock_flow_pipeline_v1</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>multifamily_under_construction_proxy_central</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Central pipeline recurrence and initialization</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Month-end stock equals prior stock plus current 5+ permits minus Central modeled completions; initialize from every cohort with positive uncompleted weight in the complete current-through-age-29 permit window.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>The approved 30-month active-cohort initialization avoids an arbitrary zero opening stock. Missing active-window inputs produce null until a complete window permits reinitialization.</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>bps_5_plus_stock_flow_pipeline_v1</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>multifamily_under_construction_proxy_slow</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Slow pipeline recurrence and initialization</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Month-end stock equals prior stock plus current 5+ permits minus Slow modeled completions; initialize from every cohort with positive uncompleted weight in the complete current-through-age-35 permit window.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>The approved 36-month active-cohort initialization avoids an arbitrary zero opening stock. Missing active-window inputs produce null until a complete window permits reinitialization.</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>irs_soi_net_exemptions_per_1000_pep_v1</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>census_pep_county_population_annual</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>PEP population vintage segments</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Use Vintage 2019 for 2010-2019 and Vintage 2025 for 2020-2025, retaining July 1 source-year estimates as annual December 31 analytic endpoints.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>The segments are nonoverlapping and preserve the 2020 vintage boundary. PEP annual values are not interpolated or expanded to a higher frequency.</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>irs_soi_net_exemptions_per_1000_pep_v1</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>net_exemption_rate</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Annual population denominator</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>IRS SOI net migration exemptions for each filing-year interval divided by Census PEP resident population for the same ending year, multiplied by 1,000.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>The workbook expressly selects the interval ending year. Prior-year and ACS population denominators are not substituted, and the annual rate is not divided or carried into observed months.</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>bps_1_unit_per_1000_pep_housing_units_v1</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>census_pep_county_housing_units_annual</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>PEP housing-unit vintage segments</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Use Vintage 2019 for 2010-2019 and Vintage 2025 for 2020-2025, retaining July 1 source-year estimates as annual December 31 analytic endpoints.</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>The segments are nonoverlapping and preserve the 2020 vintage boundary. PEP annual values are not interpolated or expanded to a higher frequency.</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>bps_1_unit_per_1000_pep_housing_units_v1</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>permits_1_unit_per_1000_housing_units</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Annual housing-stock denominator</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Final annual Census BPS one-unit authorizations divided by the same-year Census PEP housing-unit estimate, multiplied by 1,000.</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>The approved rate uses the final annual BPS product and same-year PEP housing stock. Monthly permits, ACS housing units, and lagged denominators are not substituted; the output remains annual.</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>eviction_lab_county_estimates_v1</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>eviction_lab_filings_estimate_annual</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>LA eviction-source choice</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Retain official Eviction Lab annual county modeled estimates for Los Angeles County for 2000-2018. The official ETS Version 3.0 release was checked on 2026-08-16 and contains neither Los Angeles nor any California geography; the observed/validated county analysis files also provide no LA County rows.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>This preserves the expected source family without silently substituting another geography. Annual values are not interpolated or expanded to monthly observations, and the limitation remains explicit for modeling.</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>eviction_lab_county_rate_v1</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>eviction_lab_filings_rate_estimate_annual</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Annual rate denominator</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>filings_estimate divided by Eviction Lab renting_hh, multiplied by 100.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>A rate normalizes the trend for renter-household base changes while using only fields published in the same official Eviction Lab file.</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>eviction_lab_county_rate_v1</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
         <is>
           <t>eviction_lab_households_threatened_rate_estimate_annual</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Annual rate denominator</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>hh_threat_estimate divided by Eviction Lab renting_hh, multiplied by 100.</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>A rate normalizes households-threatened estimates for renter-household base changes while using only fields published in the same official Eviction Lab file.</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>active</t>
         </is>

--- a/metadata/docx_variable_audit.xlsx
+++ b/metadata/docx_variable_audit.xlsx
@@ -3726,14 +3726,14 @@
         <v>40939</v>
       </c>
       <c r="Z19" s="1" t="n">
-        <v>46173</v>
+        <v>46265</v>
       </c>
       <c r="AA19" t="n">
-        <v>24391</v>
+        <v>28920</v>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>63 missing of 24391 fact rows</t>
+          <t>806 missing of 28920 fact rows</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -4041,14 +4041,14 @@
         <v>40939</v>
       </c>
       <c r="Z22" s="1" t="n">
-        <v>46173</v>
+        <v>46265</v>
       </c>
       <c r="AA22" t="n">
-        <v>24391</v>
+        <v>28920</v>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>31 missing of 24391 fact rows</t>
+          <t>563 missing of 28920 fact rows</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -4146,14 +4146,14 @@
         <v>40939</v>
       </c>
       <c r="Z23" s="1" t="n">
-        <v>46173</v>
+        <v>46265</v>
       </c>
       <c r="AA23" t="n">
-        <v>24391</v>
+        <v>28920</v>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>63 missing of 24391 fact rows</t>
+          <t>806 missing of 28920 fact rows</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -5188,14 +5188,14 @@
         <v>40939</v>
       </c>
       <c r="Z33" s="1" t="n">
-        <v>46173</v>
+        <v>46265</v>
       </c>
       <c r="AA33" t="n">
-        <v>24391</v>
+        <v>28920</v>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>63 missing of 24391 fact rows</t>
+          <t>813 missing of 28920 fact rows</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
